--- a/artfynd/A 4146-2025 artfynd.xlsx
+++ b/artfynd/A 4146-2025 artfynd.xlsx
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97364403</v>
+        <v>97364401</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fyråsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530925.0129475582</v>
+        <v>530911</v>
       </c>
       <c r="R2" t="n">
-        <v>7031382.309167063</v>
+        <v>7031398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +752,11 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +765,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97364433</v>
+        <v>97364421</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530931.3498742006</v>
+        <v>530969</v>
       </c>
       <c r="R3" t="n">
-        <v>7031376.545724463</v>
+        <v>7031333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +853,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,16 +889,11 @@
         <v>97364432</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530893.2755007255</v>
+        <v>530893</v>
       </c>
       <c r="R4" t="n">
-        <v>7031463.099146404</v>
+        <v>7031463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,19 +954,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,12 +990,7 @@
         <v>97364418</v>
       </c>
       <c r="B5" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530961.4245468302</v>
+        <v>530961</v>
       </c>
       <c r="R5" t="n">
-        <v>7031375.044377161</v>
+        <v>7031375</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1055,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,37 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97364428</v>
+        <v>97364424</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530895.9813960871</v>
+        <v>531181</v>
       </c>
       <c r="R6" t="n">
-        <v>7031415.184460001</v>
+        <v>7031263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,21 +1156,11 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1243,7 +1172,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,37 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97364427</v>
+        <v>97364398</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530914.1119784681</v>
+        <v>530928</v>
       </c>
       <c r="R7" t="n">
-        <v>7031396.093441712</v>
+        <v>7031377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,21 +1262,11 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1364,7 +1278,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1386,37 +1300,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97364421</v>
+        <v>97364427</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530969.9072606134</v>
+        <v>530914</v>
       </c>
       <c r="R8" t="n">
-        <v>7031333.009102496</v>
+        <v>7031396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,21 +1368,11 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1482,6 +1381,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1502,37 +1406,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97364431</v>
+        <v>97364428</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530926.1968538727</v>
+        <v>530896</v>
       </c>
       <c r="R9" t="n">
-        <v>7031445.495462903</v>
+        <v>7031415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,21 +1474,11 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1598,6 +1487,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1618,15 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97364424</v>
+        <v>97364425</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>531180.5569335647</v>
+        <v>530915</v>
       </c>
       <c r="R10" t="n">
-        <v>7031263.812466772</v>
+        <v>7031396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,21 +1580,11 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1717,7 +1596,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1739,15 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97364401</v>
+        <v>97364400</v>
       </c>
       <c r="B11" t="n">
-        <v>85177</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,43 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>445</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fyråsberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530910.9500391851</v>
+        <v>530983</v>
       </c>
       <c r="R11" t="n">
-        <v>7031398.303148546</v>
+        <v>7031258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,19 +1686,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,37 +1719,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97364425</v>
+        <v>97364431</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1904,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530915.0092068055</v>
+        <v>530926</v>
       </c>
       <c r="R12" t="n">
-        <v>7031396.102110444</v>
+        <v>7031445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,21 +1787,11 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1960,11 +1800,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1985,15 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97364400</v>
+        <v>97364433</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530982.7445254723</v>
+        <v>530931</v>
       </c>
       <c r="R13" t="n">
-        <v>7031258.306475276</v>
+        <v>7031377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,19 +1888,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,15 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97364398</v>
+        <v>97364403</v>
       </c>
       <c r="B14" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2141,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530928.2095557796</v>
+        <v>530925</v>
       </c>
       <c r="R14" t="n">
-        <v>7031376.515369012</v>
+        <v>7031383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2174,19 +1989,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 4146-2025 artfynd.xlsx
+++ b/artfynd/A 4146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364432</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364418</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364424</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364398</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364427</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364428</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364425</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364400</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364431</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364433</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2024,8 +2089,28 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>